--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/NARMADA.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/NARMADA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\ICS\2.0   PLANNING 2026-27\Kharif 2026-27\2.0\2.0 planning 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACFE256-94BA-495E-9894-EEC786ED1AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EF0F01-EC40-4881-B56B-2022C26302A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -403,12 +401,48 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -425,42 +459,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -745,72 +743,72 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.75" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-    </row>
-    <row r="2" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+    </row>
+    <row r="2" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-    </row>
-    <row r="3" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+    </row>
+    <row r="3" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+    </row>
+    <row r="4" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="23" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="13">
@@ -837,36 +835,36 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="17" t="s">
+    <row r="5" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18" t="s">
+      <c r="E5" s="15"/>
+      <c r="F5" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="17" t="s">
+      <c r="G5" s="17"/>
+      <c r="H5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17" t="s">
+      <c r="I5" s="15"/>
+      <c r="J5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17" t="s">
+      <c r="K5" s="15"/>
+      <c r="L5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="17"/>
+      <c r="M5" s="15"/>
       <c r="N5" s="1">
         <f>D4+F4+H4+J4+L4</f>
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="32.6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -908,7 +906,7 @@
       </c>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -924,7 +922,7 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>13</v>
       </c>
@@ -960,502 +958,502 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+    </row>
+    <row r="10" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="21">
-        <v>2</v>
-      </c>
-      <c r="E10" s="24">
-        <v>2</v>
-      </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="N10" s="21"/>
-    </row>
-    <row r="11" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="D10" s="6">
+        <v>2</v>
+      </c>
+      <c r="E10" s="9">
+        <v>2</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21">
-        <v>2</v>
-      </c>
-      <c r="G11" s="24">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6">
+        <v>2</v>
+      </c>
+      <c r="G11" s="9">
         <v>1</v>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
-      <c r="N11" s="21"/>
-    </row>
-    <row r="12" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21">
-        <v>2</v>
-      </c>
-      <c r="I12" s="24">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
+        <v>2</v>
+      </c>
+      <c r="I12" s="9">
         <v>3</v>
       </c>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21"/>
-    </row>
-    <row r="13" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21">
-        <v>2</v>
-      </c>
-      <c r="M13" s="24">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6">
+        <v>2</v>
+      </c>
+      <c r="M13" s="9">
         <v>3</v>
       </c>
-      <c r="N13" s="21"/>
-    </row>
-    <row r="14" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21">
-        <v>2</v>
-      </c>
-      <c r="M14" s="24">
-        <v>2</v>
-      </c>
-      <c r="N14" s="21"/>
-    </row>
-    <row r="15" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6">
+        <v>2</v>
+      </c>
+      <c r="M14" s="9">
+        <v>2</v>
+      </c>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="21">
-        <v>2</v>
-      </c>
-      <c r="E15" s="24">
+      <c r="D15" s="6">
+        <v>2</v>
+      </c>
+      <c r="E15" s="9">
         <v>1</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
-      <c r="N15" s="21"/>
-    </row>
-    <row r="16" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21">
-        <v>2</v>
-      </c>
-      <c r="G16" s="24">
-        <v>2</v>
-      </c>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
-    </row>
-    <row r="17" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6">
+        <v>2</v>
+      </c>
+      <c r="G16" s="9">
+        <v>2</v>
+      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21">
-        <v>2</v>
-      </c>
-      <c r="K17" s="24">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6">
+        <v>2</v>
+      </c>
+      <c r="K17" s="9">
         <v>4</v>
       </c>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
-      <c r="N17" s="21"/>
-    </row>
-    <row r="18" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="21">
-        <v>2</v>
-      </c>
-      <c r="M18" s="24">
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6">
+        <v>2</v>
+      </c>
+      <c r="M18" s="9">
         <v>1</v>
       </c>
-      <c r="N18" s="21"/>
-    </row>
-    <row r="19" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="21" t="s">
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21">
-        <v>2</v>
-      </c>
-      <c r="I19" s="24">
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6">
+        <v>2</v>
+      </c>
+      <c r="I19" s="9">
         <v>4</v>
       </c>
-      <c r="J19" s="21"/>
-      <c r="K19" s="21"/>
-      <c r="L19" s="21"/>
-      <c r="M19" s="21"/>
-      <c r="N19" s="21"/>
-    </row>
-    <row r="20" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="21">
-        <v>2</v>
-      </c>
-      <c r="E20" s="24">
+      <c r="D20" s="6">
+        <v>2</v>
+      </c>
+      <c r="E20" s="9">
         <v>3</v>
       </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-      <c r="K20" s="21"/>
-      <c r="L20" s="21"/>
-      <c r="M20" s="21"/>
-      <c r="N20" s="21"/>
-    </row>
-    <row r="21" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="21" t="s">
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-      <c r="K21" s="21"/>
-      <c r="L21" s="21">
-        <v>2</v>
-      </c>
-      <c r="M21" s="24">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6">
+        <v>2</v>
+      </c>
+      <c r="M21" s="9">
         <v>4</v>
       </c>
-      <c r="N21" s="21"/>
-    </row>
-    <row r="22" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21">
-        <v>2</v>
-      </c>
-      <c r="K22" s="24">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6">
+        <v>2</v>
+      </c>
+      <c r="K22" s="9">
         <v>3</v>
       </c>
-      <c r="L22" s="21"/>
-      <c r="M22" s="21"/>
-      <c r="N22" s="21"/>
-    </row>
-    <row r="23" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21">
-        <v>2</v>
-      </c>
-      <c r="I23" s="24">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6">
+        <v>2</v>
+      </c>
+      <c r="I23" s="9">
         <v>5</v>
       </c>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="21"/>
-      <c r="M23" s="21"/>
-      <c r="N23" s="21"/>
-    </row>
-    <row r="24" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="21" t="s">
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21">
-        <v>2</v>
-      </c>
-      <c r="I24" s="24">
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6">
+        <v>2</v>
+      </c>
+      <c r="I24" s="9">
         <v>1</v>
       </c>
-      <c r="J24" s="21"/>
-      <c r="K24" s="21"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="21"/>
-      <c r="N24" s="21"/>
-    </row>
-    <row r="25" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="21" t="s">
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21">
-        <v>2</v>
-      </c>
-      <c r="K25" s="24">
-        <v>2</v>
-      </c>
-      <c r="L25" s="21"/>
-      <c r="M25" s="21"/>
-      <c r="N25" s="21"/>
-    </row>
-    <row r="26" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6">
+        <v>2</v>
+      </c>
+      <c r="K25" s="9">
+        <v>2</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="21"/>
-      <c r="L26" s="21">
-        <v>2</v>
-      </c>
-      <c r="M26" s="24">
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6">
+        <v>2</v>
+      </c>
+      <c r="M26" s="9">
         <v>5</v>
       </c>
-      <c r="N26" s="21"/>
-    </row>
-    <row r="27" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="21" t="s">
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21">
-        <v>2</v>
-      </c>
-      <c r="I27" s="24">
-        <v>2</v>
-      </c>
-      <c r="J27" s="21">
-        <v>2</v>
-      </c>
-      <c r="K27" s="24">
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6">
+        <v>2</v>
+      </c>
+      <c r="I27" s="9">
+        <v>2</v>
+      </c>
+      <c r="J27" s="6">
+        <v>2</v>
+      </c>
+      <c r="K27" s="9">
         <v>1</v>
       </c>
-      <c r="L27" s="21"/>
-      <c r="M27" s="21"/>
-      <c r="N27" s="21"/>
-    </row>
-    <row r="28" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A28" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="16"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="12"/>
       <c r="D28" s="4">
         <v>6</v>
       </c>
@@ -1481,12 +1479,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+    <row r="29" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A29" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="16"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="12"/>
       <c r="D29" s="4">
         <f>+D8+D28</f>
         <v>6</v>
@@ -1519,15 +1517,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -1538,6 +1527,15 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1546,71 +1544,71 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-    </row>
-    <row r="2" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+    </row>
+    <row r="2" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-    </row>
-    <row r="3" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+    </row>
+    <row r="3" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+    </row>
+    <row r="4" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="23" t="s">
         <v>18</v>
       </c>
       <c r="D4" s="13">
@@ -1637,36 +1635,36 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="17" t="s">
+    <row r="5" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18" t="s">
+      <c r="E5" s="15"/>
+      <c r="F5" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="17" t="s">
+      <c r="G5" s="17"/>
+      <c r="H5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17" t="s">
+      <c r="I5" s="15"/>
+      <c r="J5" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17" t="s">
+      <c r="K5" s="15"/>
+      <c r="L5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="17"/>
+      <c r="M5" s="15"/>
       <c r="N5" s="1">
         <f>D4+F4+H4+J4+L4</f>
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="32.6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1708,63 +1706,63 @@
       </c>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+    <row r="7" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="20">
-        <v>2</v>
-      </c>
-      <c r="E7" s="22">
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7">
         <v>1</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20">
-        <v>2</v>
-      </c>
-      <c r="M7" s="22">
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+      <c r="M7" s="7">
         <v>1</v>
       </c>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20">
-        <v>2</v>
-      </c>
-      <c r="M8" s="22">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5">
+        <v>2</v>
+      </c>
+      <c r="M8" s="7">
         <v>2</v>
       </c>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>13</v>
       </c>
@@ -1799,212 +1797,212 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+    </row>
+    <row r="11" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="21">
-        <v>2</v>
-      </c>
-      <c r="K11" s="24">
-        <v>2</v>
-      </c>
-      <c r="L11" s="21"/>
-      <c r="M11" s="21"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="6">
+        <v>2</v>
+      </c>
+      <c r="K11" s="9">
+        <v>2</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+    <row r="12" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="21">
-        <v>2</v>
-      </c>
-      <c r="E12" s="24">
-        <v>2</v>
-      </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
+      <c r="D12" s="6">
+        <v>2</v>
+      </c>
+      <c r="E12" s="9">
+        <v>2</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+    <row r="13" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21">
-        <v>2</v>
-      </c>
-      <c r="M13" s="24">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6">
+        <v>2</v>
+      </c>
+      <c r="M13" s="9">
         <v>3</v>
       </c>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+    <row r="14" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="21">
-        <v>2</v>
-      </c>
-      <c r="K14" s="24">
+      <c r="D14" s="6"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="6">
+        <v>2</v>
+      </c>
+      <c r="K14" s="9">
         <v>1</v>
       </c>
-      <c r="L14" s="21"/>
-      <c r="M14" s="21"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+    <row r="15" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="21">
-        <v>2</v>
-      </c>
-      <c r="K15" s="24">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="6">
+        <v>2</v>
+      </c>
+      <c r="K15" s="9">
         <v>3</v>
       </c>
-      <c r="L15" s="21"/>
-      <c r="M15" s="21"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+    <row r="16" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21">
-        <v>2</v>
-      </c>
-      <c r="I16" s="24">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6">
+        <v>2</v>
+      </c>
+      <c r="I16" s="9">
         <v>1</v>
       </c>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+    <row r="17" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21">
-        <v>2</v>
-      </c>
-      <c r="I17" s="24">
-        <v>2</v>
-      </c>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
-      <c r="L17" s="21"/>
-      <c r="M17" s="21"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6">
+        <v>2</v>
+      </c>
+      <c r="I17" s="9">
+        <v>2</v>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+    <row r="18" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="16"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="4">
         <v>2</v>
       </c>
@@ -2030,12 +2028,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="12"/>
       <c r="D19" s="4">
         <f>+D9+D18</f>
         <v>4</v>
@@ -2066,15 +2064,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="A9:C9"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -2085,6 +2074,15 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A9:C9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/NARMADA.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/NARMADA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EF0F01-EC40-4881-B56B-2022C26302A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35B6F1C-9DF8-486E-B986-577CDD543DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="63">
   <si>
     <t xml:space="preserve">                               GUJARAT                                              STATEMENT NO. 4                                                  CENTRAL                                                                                      </t>
   </si>
@@ -200,6 +200,30 @@
   </si>
   <si>
     <t>PADDY(UI)</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t>5B</t>
+  </si>
+  <si>
+    <t>3A</t>
   </si>
 </sst>
 </file>
@@ -416,6 +440,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -425,20 +452,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -743,13 +767,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.75" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -767,7 +792,7 @@
       <c r="M1" s="18"/>
       <c r="N1" s="18"/>
     </row>
-    <row r="2" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -785,25 +810,25 @@
       <c r="M2" s="18"/>
       <c r="N2" s="18"/>
     </row>
-    <row r="3" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-    </row>
-    <row r="4" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
@@ -811,60 +836,60 @@
       <c r="C4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="17">
         <v>6</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17">
         <v>4</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17">
         <v>10</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13">
+      <c r="I4" s="17"/>
+      <c r="J4" s="17">
         <v>8</v>
       </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13">
+      <c r="K4" s="17"/>
+      <c r="L4" s="17">
         <v>10</v>
       </c>
-      <c r="M4" s="13"/>
+      <c r="M4" s="17"/>
       <c r="N4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="21"/>
       <c r="B5" s="22"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="15" t="s">
+      <c r="G5" s="16"/>
+      <c r="H5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="14"/>
+      <c r="J5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="14"/>
+      <c r="L5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="15"/>
+      <c r="M5" s="14"/>
       <c r="N5" s="1">
         <f>D4+F4+H4+J4+L4</f>
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="32.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,7 +931,7 @@
       </c>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -922,12 +947,12 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
       <c r="D8" s="4">
         <f>SUM(D7:D7)</f>
         <v>0</v>
@@ -958,25 +983,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-    </row>
-    <row r="10" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
@@ -1002,7 +1027,7 @@
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>20</v>
       </c>
@@ -1028,7 +1053,7 @@
       <c r="M11" s="6"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>23</v>
       </c>
@@ -1054,7 +1079,7 @@
       <c r="M12" s="6"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>23</v>
       </c>
@@ -1075,12 +1100,12 @@
       <c r="L13" s="6">
         <v>2</v>
       </c>
-      <c r="M13" s="9">
-        <v>3</v>
+      <c r="M13" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>23</v>
       </c>
@@ -1101,12 +1126,12 @@
       <c r="L14" s="6">
         <v>2</v>
       </c>
-      <c r="M14" s="9">
-        <v>2</v>
+      <c r="M14" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="N14" s="6"/>
     </row>
-    <row r="15" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
@@ -1132,7 +1157,7 @@
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>23</v>
       </c>
@@ -1158,7 +1183,7 @@
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>29</v>
       </c>
@@ -1177,14 +1202,14 @@
       <c r="J17" s="6">
         <v>2</v>
       </c>
-      <c r="K17" s="9">
-        <v>4</v>
+      <c r="K17" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>29</v>
       </c>
@@ -1205,12 +1230,12 @@
       <c r="L18" s="6">
         <v>2</v>
       </c>
-      <c r="M18" s="9">
-        <v>1</v>
+      <c r="M18" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>29</v>
       </c>
@@ -1236,7 +1261,7 @@
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>29</v>
       </c>
@@ -1262,7 +1287,7 @@
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>34</v>
       </c>
@@ -1283,12 +1308,12 @@
       <c r="L21" s="6">
         <v>2</v>
       </c>
-      <c r="M21" s="9">
-        <v>4</v>
+      <c r="M21" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>34</v>
       </c>
@@ -1307,14 +1332,14 @@
       <c r="J22" s="6">
         <v>2</v>
       </c>
-      <c r="K22" s="9">
-        <v>3</v>
+      <c r="K22" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
@@ -1340,7 +1365,7 @@
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>37</v>
       </c>
@@ -1366,7 +1391,7 @@
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>37</v>
       </c>
@@ -1385,14 +1410,14 @@
       <c r="J25" s="6">
         <v>2</v>
       </c>
-      <c r="K25" s="9">
-        <v>2</v>
+      <c r="K25" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
@@ -1413,12 +1438,12 @@
       <c r="L26" s="6">
         <v>2</v>
       </c>
-      <c r="M26" s="9">
-        <v>5</v>
+      <c r="M26" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>42</v>
       </c>
@@ -1441,19 +1466,19 @@
       <c r="J27" s="6">
         <v>2</v>
       </c>
-      <c r="K27" s="9">
-        <v>1</v>
+      <c r="K27" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
-      <c r="A28" s="10" t="s">
+    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="13"/>
       <c r="D28" s="4">
         <v>6</v>
       </c>
@@ -1479,12 +1504,12 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="11"/>
-      <c r="C29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="13"/>
       <c r="D29" s="4">
         <f>+D8+D28</f>
         <v>6</v>
@@ -1544,12 +1569,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.75" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
@@ -1567,7 +1594,7 @@
       <c r="M1" s="18"/>
       <c r="N1" s="18"/>
     </row>
-    <row r="2" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -1585,25 +1612,25 @@
       <c r="M2" s="18"/>
       <c r="N2" s="18"/>
     </row>
-    <row r="3" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-    </row>
-    <row r="4" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
@@ -1611,60 +1638,60 @@
       <c r="C4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="17">
         <v>4</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13">
+      <c r="E4" s="17"/>
+      <c r="F4" s="17">
         <v>0</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13">
+      <c r="G4" s="17"/>
+      <c r="H4" s="17">
         <v>4</v>
       </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13">
+      <c r="I4" s="17"/>
+      <c r="J4" s="17">
         <v>6</v>
       </c>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13">
+      <c r="K4" s="17"/>
+      <c r="L4" s="17">
         <v>6</v>
       </c>
-      <c r="M4" s="13"/>
+      <c r="M4" s="17"/>
       <c r="N4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="21"/>
       <c r="B5" s="22"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="15" t="s">
+      <c r="G5" s="16"/>
+      <c r="H5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15" t="s">
+      <c r="I5" s="14"/>
+      <c r="J5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15" t="s">
+      <c r="K5" s="14"/>
+      <c r="L5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="15"/>
+      <c r="M5" s="14"/>
       <c r="N5" s="1">
         <f>D4+F4+H4+J4+L4</f>
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="32.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1706,7 +1733,7 @@
       </c>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
@@ -1731,12 +1758,12 @@
       <c r="L7" s="5">
         <v>2</v>
       </c>
-      <c r="M7" s="7">
-        <v>1</v>
+      <c r="M7" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
@@ -1757,17 +1784,17 @@
       <c r="L8" s="5">
         <v>2</v>
       </c>
-      <c r="M8" s="7">
-        <v>2</v>
+      <c r="M8" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
       <c r="D9" s="4">
         <f>SUM(D7:D8)</f>
         <v>2</v>
@@ -1797,25 +1824,25 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-    </row>
-    <row r="11" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
@@ -1834,14 +1861,14 @@
       <c r="J11" s="6">
         <v>2</v>
       </c>
-      <c r="K11" s="9">
-        <v>2</v>
+      <c r="K11" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>19</v>
       </c>
@@ -1867,7 +1894,7 @@
       <c r="M12" s="6"/>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>19</v>
       </c>
@@ -1888,12 +1915,12 @@
       <c r="L13" s="6">
         <v>2</v>
       </c>
-      <c r="M13" s="9">
-        <v>3</v>
+      <c r="M13" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>19</v>
       </c>
@@ -1912,14 +1939,14 @@
       <c r="J14" s="6">
         <v>2</v>
       </c>
-      <c r="K14" s="9">
-        <v>1</v>
+      <c r="K14" s="9" t="s">
+        <v>55</v>
       </c>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>19</v>
       </c>
@@ -1938,14 +1965,14 @@
       <c r="J15" s="6">
         <v>2</v>
       </c>
-      <c r="K15" s="9">
-        <v>3</v>
+      <c r="K15" s="9" t="s">
+        <v>57</v>
       </c>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>19</v>
       </c>
@@ -1971,7 +1998,7 @@
       <c r="M16" s="6"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>19</v>
       </c>
@@ -1997,12 +2024,12 @@
       <c r="M17" s="6"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
       <c r="D18" s="4">
         <v>2</v>
       </c>
@@ -2028,12 +2055,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="16.3" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="13"/>
       <c r="D19" s="4">
         <f>+D9+D18</f>
         <v>4</v>
